--- a/task-reviews/graph/task_graph_counting_articulation_point_count/task_graph_counting_articulation_point_count.xlsx
+++ b/task-reviews/graph/task_graph_counting_articulation_point_count/task_graph_counting_articulation_point_count.xlsx
@@ -154,9 +154,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -182,9 +179,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -210,9 +204,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -238,9 +229,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -266,9 +254,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -294,9 +279,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -322,9 +304,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -350,9 +329,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -378,9 +354,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -406,9 +379,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -434,9 +404,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -462,9 +429,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -490,9 +454,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -518,9 +479,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -546,9 +504,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -574,9 +529,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -602,9 +554,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -630,9 +579,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -658,9 +604,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -686,9 +629,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -714,9 +654,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -742,9 +679,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -770,9 +704,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -798,9 +729,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -826,9 +754,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -854,9 +779,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -882,9 +804,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -910,9 +829,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -938,9 +854,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -966,9 +879,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -994,9 +904,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1022,9 +929,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1050,9 +954,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1078,9 +979,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1106,9 +1004,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1134,9 +1029,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1162,9 +1054,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1190,9 +1079,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1218,9 +1104,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1246,9 +1129,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1274,9 +1154,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1302,9 +1179,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1330,9 +1204,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1358,9 +1229,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1386,9 +1254,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1414,9 +1279,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1442,9 +1304,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1470,9 +1329,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1498,9 +1354,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1526,9 +1379,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
